--- a/output/pdf_financials_xlsx/SKY.xlsx
+++ b/output/pdf_financials_xlsx/SKY.xlsx
@@ -2570,7 +2570,7 @@
         <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>14.911039</v>
       </c>
     </row>
     <row r="113">
@@ -4946,7 +4946,11 @@
           <t>Proceeds from disposition of property and equipment (note 11)</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SKY.xlsx
+++ b/output/pdf_financials_xlsx/SKY.xlsx
@@ -2570,7 +2570,7 @@
         <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>14.911039</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -4946,11 +4946,7 @@
           <t>Proceeds from disposition of property and equipment (note 11)</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>SaleOfPPE</t>
-        </is>
-      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
